--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1713,6 +1713,341 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120278807</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78262</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 43789-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>385306</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6952780</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120278811</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 43789-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>385294</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6952914</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120278809</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 43789-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>385294</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6952914</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -1718,7 +1718,7 @@
         <v>120278807</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278811</v>
+        <v>120278809</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,33 +1837,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1909,6 +1905,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278809</v>
+        <v>120278811</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,29 +1952,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2019,11 +2024,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278807</v>
+        <v>120278811</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,26 +1731,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1758,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385306</v>
+        <v>385294</v>
       </c>
       <c r="R12" t="n">
-        <v>6952780</v>
+        <v>6952914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1811,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278809</v>
+        <v>120278807</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,31 +1845,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1869,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385294</v>
+        <v>385306</v>
       </c>
       <c r="R13" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,17 +1910,13 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1936,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278811</v>
+        <v>120278809</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,33 +1951,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2024,6 +2019,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278811</v>
+        <v>120278807</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,35 +1731,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1767,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385294</v>
+        <v>385306</v>
       </c>
       <c r="R12" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1802,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1829,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278807</v>
+        <v>120278809</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,26 +1837,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1872,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385306</v>
+        <v>385294</v>
       </c>
       <c r="R13" t="n">
-        <v>6952780</v>
+        <v>6952914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,13 +1907,17 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1935,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278809</v>
+        <v>120278811</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,29 +1952,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2021,11 +2026,6 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2047,6 +2047,1789 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120443078</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>385778</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6952687</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120440707</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>385786</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6952612</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120441015</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>385668</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6952561</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120441280</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>385671</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6952639</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120443298</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>385774</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6952640</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120438102</v>
+      </c>
+      <c r="B20" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>385765</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6952564</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120438518</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>385733</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6952582</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120443858</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>385646</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6952554</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120441428</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>385656</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6952677</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120436944</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>385778</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6952556</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120442167</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>385657</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6952733</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120441474</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>385661</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6952706</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120443179</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>385808</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6952713</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120441648</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>385642</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6952727</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120442990</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>385757</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6952721</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120439074</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Östervallen, Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>385761</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6952577</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120442556</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Österbäck, Mittådalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>385676</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6952738</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120438518</v>
+        <v>120443858</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,41 +2689,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385733</v>
+        <v>385646</v>
       </c>
       <c r="R21" t="n">
-        <v>6952582</v>
+        <v>6952554</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2779,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120443858</v>
+        <v>120438518</v>
       </c>
       <c r="B22" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,50 +2800,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385646</v>
+        <v>385733</v>
       </c>
       <c r="R22" t="n">
-        <v>6952554</v>
+        <v>6952582</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3831,6 +3831,2442 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120454913</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>385878</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6952882</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120456581</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>385426</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6953104</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120456499</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>385462</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6953154</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fler hackspår i närområdet.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120457051</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Österbäck, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>385444</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6952605</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120453824</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>385740</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6952870</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120454959</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>385878</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6952882</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120454767</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>385870</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6952880</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120453860</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>385755</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6952868</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120453988</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>385767</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6952925</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120453522</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Österbäck, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>385809</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6952882</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120455648</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>385900</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6953028</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120454810</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>385870</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6952880</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120456569</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>385413</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6953117</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120454247</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>385798</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6952906</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120456148</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>385626</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6953167</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120453603</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>385766</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6952899</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120456761</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>385283</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6953005</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120454211</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>385792</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6952933</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120453401</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Österbäck, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>385850</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6952827</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120456807</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>385254</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6952909</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120456719</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>385325</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6953048</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120454238</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>385798</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6952906</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120456291</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>385636</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6953136</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278807</v>
+        <v>120278809</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,26 +1731,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1758,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385306</v>
+        <v>385294</v>
       </c>
       <c r="R12" t="n">
-        <v>6952780</v>
+        <v>6952914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,13 +1801,17 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278809</v>
+        <v>120278811</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,29 +1846,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1905,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278811</v>
+        <v>120278807</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1952,35 +1960,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1988,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385294</v>
+        <v>385306</v>
       </c>
       <c r="R14" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,6 +2031,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2050,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120443078</v>
+        <v>120441474</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385778</v>
+        <v>385661</v>
       </c>
       <c r="R15" t="n">
-        <v>6952687</v>
+        <v>6952706</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120440707</v>
+        <v>120443298</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,37 +2173,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385786</v>
+        <v>385774</v>
       </c>
       <c r="R16" t="n">
-        <v>6952612</v>
+        <v>6952640</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2259,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120441015</v>
+        <v>120443858</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,20 +2276,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2292,10 +2297,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385668</v>
+        <v>385646</v>
       </c>
       <c r="R17" t="n">
-        <v>6952561</v>
+        <v>6952554</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2366,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120441280</v>
+        <v>120441428</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2382,34 +2391,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385671</v>
+        <v>385656</v>
       </c>
       <c r="R18" t="n">
-        <v>6952639</v>
+        <v>6952677</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2468,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120443298</v>
+        <v>120441280</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2502,21 +2511,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385774</v>
+        <v>385671</v>
       </c>
       <c r="R19" t="n">
-        <v>6952640</v>
+        <v>6952639</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2575,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120438102</v>
+        <v>120438518</v>
       </c>
       <c r="B20" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2591,21 +2595,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2615,13 +2619,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385765</v>
+        <v>385733</v>
       </c>
       <c r="R20" t="n">
-        <v>6952564</v>
+        <v>6952582</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2677,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120443858</v>
+        <v>120442167</v>
       </c>
       <c r="B21" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,20 +2693,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2710,14 +2714,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385646</v>
+        <v>385657</v>
       </c>
       <c r="R21" t="n">
-        <v>6952554</v>
+        <v>6952733</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120438518</v>
+        <v>120438102</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,21 +2804,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2828,13 +2828,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385733</v>
+        <v>385765</v>
       </c>
       <c r="R22" t="n">
-        <v>6952582</v>
+        <v>6952564</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120441428</v>
+        <v>120436944</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,21 +2906,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385656</v>
+        <v>385778</v>
       </c>
       <c r="R23" t="n">
-        <v>6952677</v>
+        <v>6952556</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120436944</v>
+        <v>120442990</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,21 +3008,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385778</v>
+        <v>385757</v>
       </c>
       <c r="R24" t="n">
-        <v>6952556</v>
+        <v>6952721</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120442167</v>
+        <v>120441015</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3130,7 +3130,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385657</v>
+        <v>385668</v>
       </c>
       <c r="R25" t="n">
-        <v>6952733</v>
+        <v>6952561</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120441474</v>
+        <v>120441648</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3237,7 +3237,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385661</v>
+        <v>385642</v>
       </c>
       <c r="R26" t="n">
-        <v>6952706</v>
+        <v>6952727</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120443179</v>
+        <v>120439074</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3324,39 +3324,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385808</v>
+        <v>385761</v>
       </c>
       <c r="R27" t="n">
-        <v>6952713</v>
+        <v>6952577</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3415,10 +3410,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120441648</v>
+        <v>120440707</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3431,42 +3426,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385642</v>
+        <v>385786</v>
       </c>
       <c r="R28" t="n">
-        <v>6952727</v>
+        <v>6952612</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3522,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120442990</v>
+        <v>120443078</v>
       </c>
       <c r="B29" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3538,34 +3528,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385757</v>
+        <v>385778</v>
       </c>
       <c r="R29" t="n">
-        <v>6952721</v>
+        <v>6952687</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3624,10 +3619,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120439074</v>
+        <v>120442556</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3640,37 +3635,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385761</v>
+        <v>385676</v>
       </c>
       <c r="R30" t="n">
-        <v>6952577</v>
+        <v>6952738</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120442556</v>
+        <v>120443179</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3762,7 +3762,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385676</v>
+        <v>385808</v>
       </c>
       <c r="R31" t="n">
-        <v>6952738</v>
+        <v>6952713</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454913</v>
+        <v>120456581</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3878,13 +3878,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385878</v>
+        <v>385426</v>
       </c>
       <c r="R32" t="n">
-        <v>6952882</v>
+        <v>6953104</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120456581</v>
+        <v>120456499</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3976,7 +3976,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385426</v>
+        <v>385462</v>
       </c>
       <c r="R33" t="n">
-        <v>6953104</v>
+        <v>6953154</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4021,6 +4021,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4047,7 +4052,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120456499</v>
+        <v>120453603</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4092,13 +4097,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385462</v>
+        <v>385766</v>
       </c>
       <c r="R34" t="n">
-        <v>6953154</v>
+        <v>6952899</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,11 +4133,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120457051</v>
+        <v>120454959</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,42 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385444</v>
+        <v>385878</v>
       </c>
       <c r="R35" t="n">
-        <v>6952605</v>
+        <v>6952882</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4266,7 +4261,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120453824</v>
+        <v>120454312</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4311,13 +4306,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385740</v>
+        <v>385767</v>
       </c>
       <c r="R36" t="n">
-        <v>6952870</v>
+        <v>6952925</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4373,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120454959</v>
+        <v>120456761</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4389,37 +4384,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385878</v>
+        <v>385283</v>
       </c>
       <c r="R37" t="n">
-        <v>6952882</v>
+        <v>6953005</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120453860</v>
+        <v>120453522</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4618,22 +4618,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385755</v>
+        <v>385809</v>
       </c>
       <c r="R39" t="n">
-        <v>6952868</v>
+        <v>6952882</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120453988</v>
+        <v>120454211</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,39 +4705,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385767</v>
+        <v>385792</v>
       </c>
       <c r="R40" t="n">
-        <v>6952925</v>
+        <v>6952933</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4796,7 +4791,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120453522</v>
+        <v>120456569</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4832,19 +4827,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385809</v>
+        <v>385413</v>
       </c>
       <c r="R41" t="n">
-        <v>6952882</v>
+        <v>6953117</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -4903,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120455648</v>
+        <v>120454247</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4919,39 +4914,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385900</v>
+        <v>385798</v>
       </c>
       <c r="R42" t="n">
-        <v>6953028</v>
+        <v>6952906</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5010,10 +5000,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120454810</v>
+        <v>120456719</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,37 +5016,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385870</v>
+        <v>385325</v>
       </c>
       <c r="R43" t="n">
-        <v>6952880</v>
+        <v>6953048</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5112,7 +5107,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120456569</v>
+        <v>120457051</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5153,14 +5148,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385413</v>
+        <v>385444</v>
       </c>
       <c r="R44" t="n">
-        <v>6953117</v>
+        <v>6952605</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5219,10 +5214,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120454247</v>
+        <v>120454913</v>
       </c>
       <c r="B45" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5235,37 +5230,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385798</v>
+        <v>385878</v>
       </c>
       <c r="R45" t="n">
-        <v>6952906</v>
+        <v>6952882</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120453603</v>
+        <v>120454810</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5439,39 +5439,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385766</v>
+        <v>385870</v>
       </c>
       <c r="R47" t="n">
-        <v>6952899</v>
+        <v>6952880</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5530,7 +5525,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120456761</v>
+        <v>120456291</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5575,13 +5570,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385283</v>
+        <v>385636</v>
       </c>
       <c r="R48" t="n">
-        <v>6953005</v>
+        <v>6953136</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5637,10 +5632,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120454211</v>
+        <v>120453401</v>
       </c>
       <c r="B49" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5653,37 +5648,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385792</v>
+        <v>385850</v>
       </c>
       <c r="R49" t="n">
-        <v>6952933</v>
+        <v>6952827</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120453401</v>
+        <v>120454238</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5775,19 +5775,19 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385850</v>
+        <v>385798</v>
       </c>
       <c r="R50" t="n">
-        <v>6952827</v>
+        <v>6952906</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120456807</v>
+        <v>120455648</v>
       </c>
       <c r="B51" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5862,37 +5862,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385254</v>
+        <v>385900</v>
       </c>
       <c r="R51" t="n">
-        <v>6952909</v>
+        <v>6953028</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5948,10 +5953,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120456719</v>
+        <v>120456807</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5964,42 +5969,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385325</v>
+        <v>385254</v>
       </c>
       <c r="R52" t="n">
-        <v>6953048</v>
+        <v>6952909</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120454238</v>
+        <v>120453824</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6091,7 +6091,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385798</v>
+        <v>385740</v>
       </c>
       <c r="R53" t="n">
-        <v>6952906</v>
+        <v>6952870</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120456291</v>
+        <v>120453860</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385636</v>
+        <v>385755</v>
       </c>
       <c r="R54" t="n">
-        <v>6953136</v>
+        <v>6952868</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278809</v>
+        <v>120278811</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,29 +1731,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1799,11 +1803,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278811</v>
+        <v>120278807</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,35 +1845,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385294</v>
+        <v>385306</v>
       </c>
       <c r="R13" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,6 +1916,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1944,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278807</v>
+        <v>120278809</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,26 +1951,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385306</v>
+        <v>385294</v>
       </c>
       <c r="R14" t="n">
-        <v>6952780</v>
+        <v>6952914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,13 +2021,17 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120441474</v>
+        <v>120436944</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,42 +2066,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385661</v>
+        <v>385778</v>
       </c>
       <c r="R15" t="n">
-        <v>6952706</v>
+        <v>6952556</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120443298</v>
+        <v>120443858</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,20 +2164,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2190,10 +2185,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2202,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385774</v>
+        <v>385646</v>
       </c>
       <c r="R16" t="n">
-        <v>6952640</v>
+        <v>6952554</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2264,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120443858</v>
+        <v>120438518</v>
       </c>
       <c r="B17" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,50 +2275,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385646</v>
+        <v>385733</v>
       </c>
       <c r="R17" t="n">
-        <v>6952554</v>
+        <v>6952582</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2375,10 +2365,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120441428</v>
+        <v>120438102</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,21 +2381,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2405,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385656</v>
+        <v>385765</v>
       </c>
       <c r="R18" t="n">
-        <v>6952677</v>
+        <v>6952564</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2477,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120441280</v>
+        <v>120439074</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,37 +2483,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385671</v>
+        <v>385761</v>
       </c>
       <c r="R19" t="n">
-        <v>6952639</v>
+        <v>6952577</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120438518</v>
+        <v>120443078</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,34 +2585,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385733</v>
+        <v>385778</v>
       </c>
       <c r="R20" t="n">
-        <v>6952582</v>
+        <v>6952687</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2681,7 +2676,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120442167</v>
+        <v>120442556</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2726,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385657</v>
+        <v>385676</v>
       </c>
       <c r="R21" t="n">
-        <v>6952733</v>
+        <v>6952738</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2788,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120438102</v>
+        <v>120443298</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,34 +2799,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385765</v>
+        <v>385774</v>
       </c>
       <c r="R22" t="n">
-        <v>6952564</v>
+        <v>6952640</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120436944</v>
+        <v>120441280</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,37 +2906,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385778</v>
+        <v>385671</v>
       </c>
       <c r="R23" t="n">
-        <v>6952556</v>
+        <v>6952639</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120441015</v>
+        <v>120440707</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,42 +3110,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385668</v>
+        <v>385786</v>
       </c>
       <c r="R25" t="n">
-        <v>6952561</v>
+        <v>6952612</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3201,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120441648</v>
+        <v>120441428</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3217,39 +3212,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385642</v>
+        <v>385656</v>
       </c>
       <c r="R26" t="n">
-        <v>6952727</v>
+        <v>6952677</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3308,10 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120439074</v>
+        <v>120441015</v>
       </c>
       <c r="B27" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3324,37 +3314,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385761</v>
+        <v>385668</v>
       </c>
       <c r="R27" t="n">
-        <v>6952577</v>
+        <v>6952561</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3410,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120440707</v>
+        <v>120443179</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3426,34 +3421,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385786</v>
+        <v>385808</v>
       </c>
       <c r="R28" t="n">
-        <v>6952612</v>
+        <v>6952713</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120443078</v>
+        <v>120442167</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385778</v>
+        <v>385657</v>
       </c>
       <c r="R29" t="n">
-        <v>6952687</v>
+        <v>6952733</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120442556</v>
+        <v>120441648</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3655,7 +3655,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385676</v>
+        <v>385642</v>
       </c>
       <c r="R30" t="n">
-        <v>6952738</v>
+        <v>6952727</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120443179</v>
+        <v>120441474</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3762,7 +3762,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385808</v>
+        <v>385661</v>
       </c>
       <c r="R31" t="n">
-        <v>6952713</v>
+        <v>6952706</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3833,7 +3833,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120456581</v>
+        <v>120454238</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385426</v>
+        <v>385798</v>
       </c>
       <c r="R32" t="n">
-        <v>6953104</v>
+        <v>6952906</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120456499</v>
+        <v>120453988</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3976,7 +3976,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385462</v>
+        <v>385767</v>
       </c>
       <c r="R33" t="n">
-        <v>6953154</v>
+        <v>6952925</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4021,11 +4021,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,7 +4047,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120453603</v>
+        <v>120454913</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4088,7 +4083,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4097,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385766</v>
+        <v>385878</v>
       </c>
       <c r="R34" t="n">
-        <v>6952899</v>
+        <v>6952882</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4159,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120454959</v>
+        <v>120455648</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,37 +4170,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385878</v>
+        <v>385900</v>
       </c>
       <c r="R35" t="n">
-        <v>6952882</v>
+        <v>6953028</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120454312</v>
+        <v>120456569</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4306,13 +4306,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385767</v>
+        <v>385413</v>
       </c>
       <c r="R36" t="n">
-        <v>6952925</v>
+        <v>6953117</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120456761</v>
+        <v>120454247</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4384,39 +4384,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385283</v>
+        <v>385798</v>
       </c>
       <c r="R37" t="n">
-        <v>6953005</v>
+        <v>6952906</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4475,7 +4470,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454767</v>
+        <v>120453603</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4511,7 +4506,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4520,10 +4515,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385870</v>
+        <v>385766</v>
       </c>
       <c r="R38" t="n">
-        <v>6952880</v>
+        <v>6952899</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4582,7 +4577,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120453522</v>
+        <v>120453824</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4618,19 +4613,19 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385809</v>
+        <v>385740</v>
       </c>
       <c r="R39" t="n">
-        <v>6952882</v>
+        <v>6952870</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4689,10 +4684,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454211</v>
+        <v>120456499</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,37 +4700,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385792</v>
+        <v>385462</v>
       </c>
       <c r="R40" t="n">
-        <v>6952933</v>
+        <v>6953154</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4765,6 +4765,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4791,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120456569</v>
+        <v>120456148</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4807,39 +4812,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385413</v>
+        <v>385626</v>
       </c>
       <c r="R41" t="n">
-        <v>6953117</v>
+        <v>6953167</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454247</v>
+        <v>120456719</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4914,34 +4914,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385798</v>
+        <v>385325</v>
       </c>
       <c r="R42" t="n">
-        <v>6952906</v>
+        <v>6953048</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5000,7 +5005,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120456719</v>
+        <v>120456291</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5036,7 +5041,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5045,13 +5050,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385325</v>
+        <v>385636</v>
       </c>
       <c r="R43" t="n">
-        <v>6953048</v>
+        <v>6953136</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5107,7 +5112,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120457051</v>
+        <v>120453522</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5143,7 +5148,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385444</v>
+        <v>385809</v>
       </c>
       <c r="R44" t="n">
-        <v>6952605</v>
+        <v>6952882</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5214,10 +5219,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120454913</v>
+        <v>120454959</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5230,29 +5235,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120456148</v>
+        <v>120456807</v>
       </c>
       <c r="B46" t="n">
         <v>90598</v>
@@ -5361,13 +5361,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385626</v>
+        <v>385254</v>
       </c>
       <c r="R46" t="n">
-        <v>6953167</v>
+        <v>6952909</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120456291</v>
+        <v>120454211</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5541,39 +5541,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385636</v>
+        <v>385792</v>
       </c>
       <c r="R48" t="n">
-        <v>6953136</v>
+        <v>6952933</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5632,7 +5627,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120453401</v>
+        <v>120456581</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5668,19 +5663,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385850</v>
+        <v>385426</v>
       </c>
       <c r="R49" t="n">
-        <v>6952827</v>
+        <v>6953104</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5739,7 +5734,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120454238</v>
+        <v>120453860</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5775,7 +5770,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5784,13 +5779,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385798</v>
+        <v>385755</v>
       </c>
       <c r="R50" t="n">
-        <v>6952906</v>
+        <v>6952868</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5846,7 +5841,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120455648</v>
+        <v>120456761</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5891,10 +5886,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385900</v>
+        <v>385283</v>
       </c>
       <c r="R51" t="n">
-        <v>6953028</v>
+        <v>6953005</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5953,10 +5948,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120456807</v>
+        <v>120454767</v>
       </c>
       <c r="B52" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5969,37 +5964,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385254</v>
+        <v>385870</v>
       </c>
       <c r="R52" t="n">
-        <v>6952909</v>
+        <v>6952880</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120453824</v>
+        <v>120457051</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385740</v>
+        <v>385444</v>
       </c>
       <c r="R53" t="n">
-        <v>6952870</v>
+        <v>6952605</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120453860</v>
+        <v>120453401</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6203,17 +6203,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385755</v>
+        <v>385850</v>
       </c>
       <c r="R54" t="n">
-        <v>6952868</v>
+        <v>6952827</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -2152,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120443858</v>
+        <v>120438518</v>
       </c>
       <c r="B16" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,50 +2164,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385646</v>
+        <v>385733</v>
       </c>
       <c r="R16" t="n">
-        <v>6952554</v>
+        <v>6952582</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2263,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120438518</v>
+        <v>120438102</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2270,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2303,13 +2294,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385733</v>
+        <v>385765</v>
       </c>
       <c r="R17" t="n">
-        <v>6952582</v>
+        <v>6952564</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120438102</v>
+        <v>120443858</v>
       </c>
       <c r="B18" t="n">
-        <v>74654</v>
+        <v>57431</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,38 +2368,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385765</v>
+        <v>385646</v>
       </c>
       <c r="R18" t="n">
-        <v>6952564</v>
+        <v>6952554</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120441280</v>
+        <v>120442990</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,37 +2906,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385671</v>
+        <v>385757</v>
       </c>
       <c r="R23" t="n">
-        <v>6952639</v>
+        <v>6952721</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120442990</v>
+        <v>120441280</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,37 +3008,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385757</v>
+        <v>385671</v>
       </c>
       <c r="R24" t="n">
-        <v>6952721</v>
+        <v>6952639</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278811</v>
+        <v>120278807</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,35 +1731,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1767,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385294</v>
+        <v>385306</v>
       </c>
       <c r="R12" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1802,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1829,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278807</v>
+        <v>120278809</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,26 +1837,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1872,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385306</v>
+        <v>385294</v>
       </c>
       <c r="R13" t="n">
-        <v>6952780</v>
+        <v>6952914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,13 +1907,17 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1935,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278809</v>
+        <v>120278811</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,29 +1952,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2019,11 +2024,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120436944</v>
+        <v>120442990</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,21 +2066,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385778</v>
+        <v>385757</v>
       </c>
       <c r="R15" t="n">
-        <v>6952556</v>
+        <v>6952721</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120438518</v>
+        <v>120441015</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,37 +2168,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385733</v>
+        <v>385668</v>
       </c>
       <c r="R16" t="n">
-        <v>6952582</v>
+        <v>6952561</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,7 +2259,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120438102</v>
+        <v>120439074</v>
       </c>
       <c r="B17" t="n">
         <v>74654</v>
@@ -2294,13 +2299,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385765</v>
+        <v>385761</v>
       </c>
       <c r="R17" t="n">
-        <v>6952564</v>
+        <v>6952577</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2356,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120443858</v>
+        <v>120441648</v>
       </c>
       <c r="B18" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,20 +2373,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2389,14 +2394,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2405,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385646</v>
+        <v>385642</v>
       </c>
       <c r="R18" t="n">
-        <v>6952554</v>
+        <v>6952727</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2467,10 +2468,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120439074</v>
+        <v>120438518</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2483,21 +2484,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2507,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385761</v>
+        <v>385733</v>
       </c>
       <c r="R19" t="n">
-        <v>6952577</v>
+        <v>6952582</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2569,10 +2570,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120443078</v>
+        <v>120440707</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2585,39 +2586,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385778</v>
+        <v>385786</v>
       </c>
       <c r="R20" t="n">
-        <v>6952687</v>
+        <v>6952612</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2676,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120442556</v>
+        <v>120441428</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2692,39 +2688,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385676</v>
+        <v>385656</v>
       </c>
       <c r="R21" t="n">
-        <v>6952738</v>
+        <v>6952677</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2783,10 +2774,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120443298</v>
+        <v>120438102</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,39 +2790,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385774</v>
+        <v>385765</v>
       </c>
       <c r="R22" t="n">
-        <v>6952640</v>
+        <v>6952564</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2890,10 +2876,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120442990</v>
+        <v>120443078</v>
       </c>
       <c r="B23" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,34 +2892,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385757</v>
+        <v>385778</v>
       </c>
       <c r="R23" t="n">
-        <v>6952721</v>
+        <v>6952687</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2992,7 +2983,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120441280</v>
+        <v>120443298</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3026,16 +3017,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385671</v>
+        <v>385774</v>
       </c>
       <c r="R24" t="n">
-        <v>6952639</v>
+        <v>6952640</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3094,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120440707</v>
+        <v>120441474</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,34 +3106,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385786</v>
+        <v>385661</v>
       </c>
       <c r="R25" t="n">
-        <v>6952612</v>
+        <v>6952706</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3196,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120441428</v>
+        <v>120436944</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3212,21 +3213,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3236,13 +3237,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385656</v>
+        <v>385778</v>
       </c>
       <c r="R26" t="n">
-        <v>6952677</v>
+        <v>6952556</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3298,7 +3299,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120441015</v>
+        <v>120442556</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3334,7 +3335,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3343,10 +3344,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385668</v>
+        <v>385676</v>
       </c>
       <c r="R27" t="n">
-        <v>6952561</v>
+        <v>6952738</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3512,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120442167</v>
+        <v>120443858</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3524,20 +3525,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3545,10 +3546,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385657</v>
+        <v>385646</v>
       </c>
       <c r="R29" t="n">
-        <v>6952733</v>
+        <v>6952554</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3619,7 +3624,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120441648</v>
+        <v>120442167</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3655,7 +3660,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3664,10 +3669,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385642</v>
+        <v>385657</v>
       </c>
       <c r="R30" t="n">
-        <v>6952727</v>
+        <v>6952733</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3726,7 +3731,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120441474</v>
+        <v>120441280</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3760,24 +3765,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385661</v>
+        <v>385671</v>
       </c>
       <c r="R31" t="n">
-        <v>6952706</v>
+        <v>6952639</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3833,10 +3833,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454238</v>
+        <v>120456807</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,42 +3849,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385798</v>
+        <v>385254</v>
       </c>
       <c r="R32" t="n">
-        <v>6952906</v>
+        <v>6952909</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3940,10 +3935,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453988</v>
+        <v>120454247</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,42 +3951,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385767</v>
+        <v>385798</v>
       </c>
       <c r="R33" t="n">
-        <v>6952925</v>
+        <v>6952906</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4047,7 +4037,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120454913</v>
+        <v>120455648</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4083,7 +4073,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4092,13 +4082,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385878</v>
+        <v>385900</v>
       </c>
       <c r="R34" t="n">
-        <v>6952882</v>
+        <v>6953028</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4154,7 +4144,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120455648</v>
+        <v>120454312</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4199,13 +4189,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385900</v>
+        <v>385767</v>
       </c>
       <c r="R35" t="n">
-        <v>6953028</v>
+        <v>6952925</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4261,7 +4251,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120456569</v>
+        <v>120456291</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4306,13 +4296,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385413</v>
+        <v>385636</v>
       </c>
       <c r="R36" t="n">
-        <v>6953117</v>
+        <v>6953136</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4368,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120454247</v>
+        <v>120456761</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4384,34 +4374,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385798</v>
+        <v>385283</v>
       </c>
       <c r="R37" t="n">
-        <v>6952906</v>
+        <v>6953005</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4470,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120453603</v>
+        <v>120454810</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4486,39 +4481,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385766</v>
+        <v>385870</v>
       </c>
       <c r="R38" t="n">
-        <v>6952899</v>
+        <v>6952880</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4577,7 +4567,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120453824</v>
+        <v>120454913</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4613,7 +4603,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4622,13 +4612,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385740</v>
+        <v>385878</v>
       </c>
       <c r="R39" t="n">
-        <v>6952870</v>
+        <v>6952882</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4684,7 +4674,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120456499</v>
+        <v>120454767</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4720,7 +4710,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4729,13 +4719,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385462</v>
+        <v>385870</v>
       </c>
       <c r="R40" t="n">
-        <v>6953154</v>
+        <v>6952880</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4765,11 +4755,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4796,10 +4781,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120456148</v>
+        <v>120454238</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4812,34 +4797,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385626</v>
+        <v>385798</v>
       </c>
       <c r="R41" t="n">
-        <v>6953167</v>
+        <v>6952906</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -4898,10 +4888,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120456719</v>
+        <v>120454959</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4914,42 +4904,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385325</v>
+        <v>385878</v>
       </c>
       <c r="R42" t="n">
-        <v>6953048</v>
+        <v>6952882</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5005,10 +4990,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120456291</v>
+        <v>120456148</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,42 +5006,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385636</v>
+        <v>385626</v>
       </c>
       <c r="R43" t="n">
-        <v>6953136</v>
+        <v>6953167</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5112,7 +5092,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120453522</v>
+        <v>120456499</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5148,22 +5128,22 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385809</v>
+        <v>385462</v>
       </c>
       <c r="R44" t="n">
-        <v>6952882</v>
+        <v>6953154</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5193,6 +5173,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,10 +5204,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120454959</v>
+        <v>120453603</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5235,34 +5220,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385878</v>
+        <v>385766</v>
       </c>
       <c r="R45" t="n">
-        <v>6952882</v>
+        <v>6952899</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5321,10 +5311,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120456807</v>
+        <v>120453522</v>
       </c>
       <c r="B46" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5337,37 +5327,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385254</v>
+        <v>385809</v>
       </c>
       <c r="R46" t="n">
-        <v>6952909</v>
+        <v>6952882</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5423,10 +5418,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120454810</v>
+        <v>120453401</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5439,37 +5434,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385870</v>
+        <v>385850</v>
       </c>
       <c r="R47" t="n">
-        <v>6952880</v>
+        <v>6952827</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120456581</v>
+        <v>120453824</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5663,7 +5663,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385426</v>
+        <v>385740</v>
       </c>
       <c r="R49" t="n">
-        <v>6953104</v>
+        <v>6952870</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120453860</v>
+        <v>120457051</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5775,17 +5775,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385755</v>
+        <v>385444</v>
       </c>
       <c r="R50" t="n">
-        <v>6952868</v>
+        <v>6952605</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120456761</v>
+        <v>120456569</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385283</v>
+        <v>385413</v>
       </c>
       <c r="R51" t="n">
-        <v>6953005</v>
+        <v>6953117</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120454767</v>
+        <v>120456719</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -5993,13 +5993,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385870</v>
+        <v>385325</v>
       </c>
       <c r="R52" t="n">
-        <v>6952880</v>
+        <v>6953048</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120457051</v>
+        <v>120456581</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6091,19 +6091,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385444</v>
+        <v>385426</v>
       </c>
       <c r="R53" t="n">
-        <v>6952605</v>
+        <v>6953104</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120453401</v>
+        <v>120453860</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6203,17 +6203,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385850</v>
+        <v>385755</v>
       </c>
       <c r="R54" t="n">
-        <v>6952827</v>
+        <v>6952868</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278807</v>
+        <v>120278809</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,26 +1731,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1758,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385306</v>
+        <v>385294</v>
       </c>
       <c r="R12" t="n">
-        <v>6952780</v>
+        <v>6952914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,13 +1801,17 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278809</v>
+        <v>120278807</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,31 +1846,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1869,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385294</v>
+        <v>385306</v>
       </c>
       <c r="R13" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,17 +1911,13 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120442990</v>
+        <v>120436944</v>
       </c>
       <c r="B15" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,21 +2066,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385757</v>
+        <v>385778</v>
       </c>
       <c r="R15" t="n">
-        <v>6952721</v>
+        <v>6952556</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120441015</v>
+        <v>120441280</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2186,21 +2186,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385668</v>
+        <v>385671</v>
       </c>
       <c r="R16" t="n">
-        <v>6952561</v>
+        <v>6952639</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2259,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120439074</v>
+        <v>120443179</v>
       </c>
       <c r="B17" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,34 +2270,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385761</v>
+        <v>385808</v>
       </c>
       <c r="R17" t="n">
-        <v>6952577</v>
+        <v>6952713</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120441648</v>
+        <v>120441428</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,39 +2377,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385642</v>
+        <v>385656</v>
       </c>
       <c r="R18" t="n">
-        <v>6952727</v>
+        <v>6952677</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120438518</v>
+        <v>120441648</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2484,37 +2479,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385733</v>
+        <v>385642</v>
       </c>
       <c r="R19" t="n">
-        <v>6952582</v>
+        <v>6952727</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120440707</v>
+        <v>120443078</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2586,34 +2586,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385786</v>
+        <v>385778</v>
       </c>
       <c r="R20" t="n">
-        <v>6952612</v>
+        <v>6952687</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2672,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120441428</v>
+        <v>120441474</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2688,37 +2693,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385656</v>
+        <v>385661</v>
       </c>
       <c r="R21" t="n">
-        <v>6952677</v>
+        <v>6952706</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2774,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120438102</v>
+        <v>120441015</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2790,34 +2800,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385765</v>
+        <v>385668</v>
       </c>
       <c r="R22" t="n">
-        <v>6952564</v>
+        <v>6952561</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2876,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120443078</v>
+        <v>120440707</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2892,39 +2907,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385778</v>
+        <v>385786</v>
       </c>
       <c r="R23" t="n">
-        <v>6952687</v>
+        <v>6952612</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2983,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120443298</v>
+        <v>120438102</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,39 +3009,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385774</v>
+        <v>385765</v>
       </c>
       <c r="R24" t="n">
-        <v>6952640</v>
+        <v>6952564</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3090,7 +3095,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120441474</v>
+        <v>120442167</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3135,13 +3140,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385661</v>
+        <v>385657</v>
       </c>
       <c r="R25" t="n">
-        <v>6952706</v>
+        <v>6952733</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3197,10 +3202,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120436944</v>
+        <v>120443858</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,41 +3214,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385778</v>
+        <v>385646</v>
       </c>
       <c r="R26" t="n">
-        <v>6952556</v>
+        <v>6952554</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3299,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120442556</v>
+        <v>120442990</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,42 +3329,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385676</v>
+        <v>385757</v>
       </c>
       <c r="R27" t="n">
-        <v>6952738</v>
+        <v>6952721</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3406,7 +3415,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120443179</v>
+        <v>120443298</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3451,13 +3460,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385808</v>
+        <v>385774</v>
       </c>
       <c r="R28" t="n">
-        <v>6952713</v>
+        <v>6952640</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3513,10 +3522,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120443858</v>
+        <v>120438518</v>
       </c>
       <c r="B29" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,50 +3534,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385646</v>
+        <v>385733</v>
       </c>
       <c r="R29" t="n">
-        <v>6952554</v>
+        <v>6952582</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120442167</v>
+        <v>120439074</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3640,42 +3640,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385657</v>
+        <v>385761</v>
       </c>
       <c r="R30" t="n">
-        <v>6952733</v>
+        <v>6952577</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3731,7 +3726,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120441280</v>
+        <v>120442556</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3765,16 +3760,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385671</v>
+        <v>385676</v>
       </c>
       <c r="R31" t="n">
-        <v>6952639</v>
+        <v>6952738</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3833,10 +3833,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120456807</v>
+        <v>120456761</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,37 +3849,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385254</v>
+        <v>385283</v>
       </c>
       <c r="R32" t="n">
-        <v>6952909</v>
+        <v>6953005</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3935,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120454247</v>
+        <v>120456719</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3951,34 +3956,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385798</v>
+        <v>385325</v>
       </c>
       <c r="R33" t="n">
-        <v>6952906</v>
+        <v>6953048</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4037,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120455648</v>
+        <v>120456807</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4053,42 +4063,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385900</v>
+        <v>385254</v>
       </c>
       <c r="R34" t="n">
-        <v>6953028</v>
+        <v>6952909</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120454312</v>
+        <v>120456581</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4180,7 +4185,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4189,13 +4194,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385767</v>
+        <v>385426</v>
       </c>
       <c r="R35" t="n">
-        <v>6952925</v>
+        <v>6953104</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4251,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120456291</v>
+        <v>120456148</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,42 +4272,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385636</v>
+        <v>385626</v>
       </c>
       <c r="R36" t="n">
-        <v>6953136</v>
+        <v>6953167</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120456761</v>
+        <v>120455648</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385283</v>
+        <v>385900</v>
       </c>
       <c r="R37" t="n">
-        <v>6953005</v>
+        <v>6953028</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454810</v>
+        <v>120456499</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4481,37 +4481,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385870</v>
+        <v>385462</v>
       </c>
       <c r="R38" t="n">
-        <v>6952880</v>
+        <v>6953154</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4541,6 +4546,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,7 +4577,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120454913</v>
+        <v>120453988</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4612,10 +4622,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385878</v>
+        <v>385767</v>
       </c>
       <c r="R39" t="n">
-        <v>6952882</v>
+        <v>6952925</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4674,7 +4684,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454767</v>
+        <v>120453401</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4710,22 +4720,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385870</v>
+        <v>385850</v>
       </c>
       <c r="R40" t="n">
-        <v>6952880</v>
+        <v>6952827</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4781,10 +4791,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120454238</v>
+        <v>120454810</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4797,42 +4807,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385798</v>
+        <v>385870</v>
       </c>
       <c r="R41" t="n">
-        <v>6952906</v>
+        <v>6952880</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4888,10 +4893,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454959</v>
+        <v>120453522</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4904,37 +4909,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385878</v>
+        <v>385809</v>
       </c>
       <c r="R42" t="n">
         <v>6952882</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4990,10 +5000,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120456148</v>
+        <v>120457051</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5006,34 +5016,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385626</v>
+        <v>385444</v>
       </c>
       <c r="R43" t="n">
-        <v>6953167</v>
+        <v>6952605</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5092,7 +5107,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120456499</v>
+        <v>120453860</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5137,13 +5152,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385462</v>
+        <v>385755</v>
       </c>
       <c r="R44" t="n">
-        <v>6953154</v>
+        <v>6952868</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5173,11 +5188,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5204,10 +5214,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120453603</v>
+        <v>120454247</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5220,42 +5230,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385766</v>
+        <v>385798</v>
       </c>
       <c r="R45" t="n">
-        <v>6952899</v>
+        <v>6952906</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5311,7 +5316,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120453522</v>
+        <v>120456291</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5347,22 +5352,22 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385809</v>
+        <v>385636</v>
       </c>
       <c r="R46" t="n">
-        <v>6952882</v>
+        <v>6953136</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5418,7 +5423,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120453401</v>
+        <v>120453603</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5459,17 +5464,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385850</v>
+        <v>385766</v>
       </c>
       <c r="R47" t="n">
-        <v>6952827</v>
+        <v>6952899</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5525,10 +5530,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120454211</v>
+        <v>120454767</v>
       </c>
       <c r="B48" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5541,34 +5546,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385792</v>
+        <v>385870</v>
       </c>
       <c r="R48" t="n">
-        <v>6952933</v>
+        <v>6952880</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5627,7 +5637,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120453824</v>
+        <v>120456569</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5672,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385740</v>
+        <v>385413</v>
       </c>
       <c r="R49" t="n">
-        <v>6952870</v>
+        <v>6953117</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5734,7 +5744,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120457051</v>
+        <v>120453824</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5775,14 +5785,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385444</v>
+        <v>385740</v>
       </c>
       <c r="R50" t="n">
-        <v>6952605</v>
+        <v>6952870</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -5841,10 +5851,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120456569</v>
+        <v>120454211</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5857,42 +5867,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385413</v>
+        <v>385792</v>
       </c>
       <c r="R51" t="n">
-        <v>6953117</v>
+        <v>6952933</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5948,10 +5953,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120456719</v>
+        <v>120454959</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5964,42 +5969,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385325</v>
+        <v>385878</v>
       </c>
       <c r="R52" t="n">
-        <v>6953048</v>
+        <v>6952882</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120456581</v>
+        <v>120454913</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6100,13 +6100,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385426</v>
+        <v>385878</v>
       </c>
       <c r="R53" t="n">
-        <v>6953104</v>
+        <v>6952882</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120453860</v>
+        <v>120454238</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6198,7 +6198,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385755</v>
+        <v>385798</v>
       </c>
       <c r="R54" t="n">
-        <v>6952868</v>
+        <v>6952906</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -3833,10 +3833,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120456761</v>
+        <v>120456807</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,42 +3849,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385283</v>
+        <v>385254</v>
       </c>
       <c r="R32" t="n">
-        <v>6953005</v>
+        <v>6952909</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3940,7 +3935,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120456719</v>
+        <v>120456761</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3976,7 +3971,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3985,10 +3980,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385325</v>
+        <v>385283</v>
       </c>
       <c r="R33" t="n">
-        <v>6953048</v>
+        <v>6953005</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4047,10 +4042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120456807</v>
+        <v>120456719</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4063,37 +4058,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385254</v>
+        <v>385325</v>
       </c>
       <c r="R34" t="n">
-        <v>6952909</v>
+        <v>6953048</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120453860</v>
+        <v>120454247</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5123,42 +5123,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385755</v>
+        <v>385798</v>
       </c>
       <c r="R44" t="n">
-        <v>6952868</v>
+        <v>6952906</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5214,10 +5209,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120454247</v>
+        <v>120453860</v>
       </c>
       <c r="B45" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5230,37 +5225,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385798</v>
+        <v>385755</v>
       </c>
       <c r="R45" t="n">
-        <v>6952906</v>
+        <v>6952868</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112548756</v>
+        <v>112557092</v>
       </c>
       <c r="B2" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385354</v>
+        <v>385330</v>
       </c>
       <c r="R2" t="n">
-        <v>6952780</v>
+        <v>6953034</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112549397</v>
+        <v>112557239</v>
       </c>
       <c r="B3" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,13 +809,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385310</v>
+        <v>385330</v>
       </c>
       <c r="R3" t="n">
-        <v>6953183</v>
+        <v>6953034</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112548735</v>
+        <v>112549327</v>
       </c>
       <c r="B4" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,43 +882,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385339</v>
+        <v>385423</v>
       </c>
       <c r="R4" t="n">
-        <v>6952726</v>
+        <v>6953240</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,54 +969,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112556390</v>
+        <v>120436944</v>
       </c>
       <c r="B5" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385551</v>
+        <v>385778</v>
       </c>
       <c r="R5" t="n">
-        <v>6953318</v>
+        <v>6952556</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,12 +1034,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,71 +1054,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112549343</v>
+        <v>120438518</v>
       </c>
       <c r="B6" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385424</v>
+        <v>385733</v>
       </c>
       <c r="R6" t="n">
-        <v>6953240</v>
+        <v>6952582</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,12 +1131,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,66 +1151,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112548768</v>
+        <v>120440707</v>
       </c>
       <c r="B7" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385354</v>
+        <v>385786</v>
       </c>
       <c r="R7" t="n">
-        <v>6952780</v>
+        <v>6952612</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1271,12 +1228,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,66 +1248,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112557050</v>
+        <v>120454810</v>
       </c>
       <c r="B8" t="n">
-        <v>73930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385329</v>
+        <v>385870</v>
       </c>
       <c r="R8" t="n">
-        <v>6953033</v>
+        <v>6952880</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,12 +1325,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,27 +1345,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112557239</v>
+        <v>120454959</v>
       </c>
       <c r="B9" t="n">
-        <v>90101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,38 +1368,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385329</v>
+        <v>385878</v>
       </c>
       <c r="R9" t="n">
-        <v>6953033</v>
+        <v>6952882</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1477,12 +1422,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,27 +1442,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112557092</v>
+        <v>112557050</v>
       </c>
       <c r="B10" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,21 +1465,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385329</v>
+        <v>385330</v>
       </c>
       <c r="R10" t="n">
-        <v>6953033</v>
+        <v>6953034</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1612,15 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112549327</v>
+        <v>120438102</v>
       </c>
       <c r="B11" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,38 +1563,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385424</v>
+        <v>385765</v>
       </c>
       <c r="R11" t="n">
-        <v>6953240</v>
+        <v>6952564</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,12 +1617,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,27 +1637,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278811</v>
+        <v>120439074</v>
       </c>
       <c r="B12" t="n">
-        <v>57485</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,49 +1660,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 43789-2024, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385294</v>
+        <v>385761</v>
       </c>
       <c r="R12" t="n">
-        <v>6952914</v>
+        <v>6952577</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,12 +1714,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,12 +1734,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1832,12 +1749,7 @@
         <v>120278807</v>
       </c>
       <c r="B13" t="n">
-        <v>78296</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,15 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278809</v>
+        <v>112548756</v>
       </c>
       <c r="B14" t="n">
-        <v>57332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,45 +1858,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 43789-2024, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385294</v>
+        <v>385355</v>
       </c>
       <c r="R14" t="n">
-        <v>6952914</v>
+        <v>6952780</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2013,17 +1913,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,27 +1933,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120441428</v>
+        <v>112548735</v>
       </c>
       <c r="B15" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,37 +1956,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385656</v>
+        <v>385339</v>
       </c>
       <c r="R15" t="n">
-        <v>6952677</v>
+        <v>6952726</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2120,12 +2016,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,27 +2036,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120440707</v>
+        <v>112549343</v>
       </c>
       <c r="B16" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,37 +2059,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385786</v>
+        <v>385423</v>
       </c>
       <c r="R16" t="n">
-        <v>6952612</v>
+        <v>6953240</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2222,12 +2119,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2242,27 +2139,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120441474</v>
+        <v>120278809</v>
       </c>
       <c r="B17" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,24 +2180,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>A 43789-2024, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385661</v>
+        <v>385294</v>
       </c>
       <c r="R17" t="n">
-        <v>6952706</v>
+        <v>6952914</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,12 +2224,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på ca 10 träd som stod intill varandra</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2349,12 +2249,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2364,12 +2264,7 @@
         <v>120441015</v>
       </c>
       <c r="B18" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,15 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120442167</v>
+        <v>120441280</v>
       </c>
       <c r="B19" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,21 +2392,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385657</v>
+        <v>385671</v>
       </c>
       <c r="R19" t="n">
-        <v>6952733</v>
+        <v>6952639</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2575,15 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120438518</v>
+        <v>120441474</v>
       </c>
       <c r="B20" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,34 +2471,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385733</v>
+        <v>385661</v>
       </c>
       <c r="R20" t="n">
-        <v>6952582</v>
+        <v>6952706</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2677,15 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120438102</v>
+        <v>120441648</v>
       </c>
       <c r="B21" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,34 +2573,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385765</v>
+        <v>385642</v>
       </c>
       <c r="R21" t="n">
-        <v>6952564</v>
+        <v>6952727</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2779,32 +2664,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120443858</v>
+        <v>120442167</v>
       </c>
       <c r="B22" t="n">
-        <v>57455</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2812,14 +2692,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2828,10 +2704,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385646</v>
+        <v>385657</v>
       </c>
       <c r="R22" t="n">
-        <v>6952554</v>
+        <v>6952733</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2890,15 +2766,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120436944</v>
+        <v>120442556</v>
       </c>
       <c r="B23" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,37 +2777,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385778</v>
+        <v>385676</v>
       </c>
       <c r="R23" t="n">
-        <v>6952556</v>
+        <v>6952738</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2995,12 +2871,7 @@
         <v>120443078</v>
       </c>
       <c r="B24" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3099,15 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120441280</v>
+        <v>120443179</v>
       </c>
       <c r="B25" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,19 +2999,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385671</v>
+        <v>385808</v>
       </c>
       <c r="R25" t="n">
-        <v>6952639</v>
+        <v>6952713</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3204,12 +3075,7 @@
         <v>120443298</v>
       </c>
       <c r="B26" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,15 +3174,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120439074</v>
+        <v>120452681</v>
       </c>
       <c r="B27" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,34 +3185,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385761</v>
+        <v>385851</v>
       </c>
       <c r="R27" t="n">
-        <v>6952577</v>
+        <v>6952728</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3378,12 +3244,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3410,15 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120443179</v>
+        <v>120453401</v>
       </c>
       <c r="B28" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,22 +3307,22 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385808</v>
+        <v>385850</v>
       </c>
       <c r="R28" t="n">
-        <v>6952713</v>
+        <v>6952827</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3485,12 +3346,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3517,15 +3378,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120442556</v>
+        <v>120453522</v>
       </c>
       <c r="B29" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3553,19 +3409,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385676</v>
+        <v>385809</v>
       </c>
       <c r="R29" t="n">
-        <v>6952738</v>
+        <v>6952882</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3592,12 +3448,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,15 +3480,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120441648</v>
+        <v>120453603</v>
       </c>
       <c r="B30" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3660,22 +3511,22 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Österbäck, Mittådalen, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385642</v>
+        <v>385766</v>
       </c>
       <c r="R30" t="n">
-        <v>6952727</v>
+        <v>6952899</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3699,12 +3550,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3731,15 +3582,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120442990</v>
+        <v>120453824</v>
       </c>
       <c r="B31" t="n">
-        <v>79179</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,37 +3593,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östervallen, Östervallen, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385757</v>
+        <v>385740</v>
       </c>
       <c r="R31" t="n">
-        <v>6952721</v>
+        <v>6952870</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3801,12 +3652,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3833,15 +3684,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120456291</v>
+        <v>120453860</v>
       </c>
       <c r="B32" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3878,10 +3724,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385636</v>
+        <v>385755</v>
       </c>
       <c r="R32" t="n">
-        <v>6953136</v>
+        <v>6952868</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3940,15 +3786,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120453522</v>
+        <v>120453988</v>
       </c>
       <c r="B33" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,17 +3822,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385809</v>
+        <v>385767</v>
       </c>
       <c r="R33" t="n">
-        <v>6952882</v>
+        <v>6952925</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4047,15 +3888,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120453824</v>
+        <v>120454238</v>
       </c>
       <c r="B34" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4083,7 +3919,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4092,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385740</v>
+        <v>385798</v>
       </c>
       <c r="R34" t="n">
-        <v>6952870</v>
+        <v>6952906</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4154,15 +3990,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120457051</v>
+        <v>120454767</v>
       </c>
       <c r="B35" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,22 +4021,22 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385444</v>
+        <v>385870</v>
       </c>
       <c r="R35" t="n">
-        <v>6952605</v>
+        <v>6952880</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4261,15 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120456807</v>
+        <v>120454913</v>
       </c>
       <c r="B36" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4277,37 +4103,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385254</v>
+        <v>385878</v>
       </c>
       <c r="R36" t="n">
-        <v>6952909</v>
+        <v>6952882</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4363,15 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120453603</v>
+        <v>120455648</v>
       </c>
       <c r="B37" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4408,13 +4234,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385766</v>
+        <v>385900</v>
       </c>
       <c r="R37" t="n">
-        <v>6952899</v>
+        <v>6953028</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4470,15 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454238</v>
+        <v>120456291</v>
       </c>
       <c r="B38" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4506,7 +4327,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4515,13 +4336,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385798</v>
+        <v>385636</v>
       </c>
       <c r="R38" t="n">
-        <v>6952906</v>
+        <v>6953136</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4577,15 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120453860</v>
+        <v>120456499</v>
       </c>
       <c r="B39" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4622,13 +4438,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385755</v>
+        <v>385462</v>
       </c>
       <c r="R39" t="n">
-        <v>6952868</v>
+        <v>6953154</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4658,6 +4474,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,15 +4505,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120456581</v>
+        <v>120456569</v>
       </c>
       <c r="B40" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4720,7 +4536,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4729,10 +4545,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385426</v>
+        <v>385413</v>
       </c>
       <c r="R40" t="n">
-        <v>6953104</v>
+        <v>6953117</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4791,15 +4607,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120454247</v>
+        <v>120456581</v>
       </c>
       <c r="B41" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4807,34 +4618,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385798</v>
+        <v>385426</v>
       </c>
       <c r="R41" t="n">
-        <v>6952906</v>
+        <v>6953104</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -4893,15 +4709,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120456148</v>
+        <v>120456719</v>
       </c>
       <c r="B42" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4909,34 +4720,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385626</v>
+        <v>385325</v>
       </c>
       <c r="R42" t="n">
-        <v>6953167</v>
+        <v>6953048</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -4995,15 +4811,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120456499</v>
+        <v>120456761</v>
       </c>
       <c r="B43" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5040,13 +4851,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385462</v>
+        <v>385283</v>
       </c>
       <c r="R43" t="n">
-        <v>6953154</v>
+        <v>6953005</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5076,11 +4887,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fler hackspår i närområdet.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5107,15 +4913,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120454312</v>
+        <v>120457051</v>
       </c>
       <c r="B44" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5148,17 +4949,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385767</v>
+        <v>385444</v>
       </c>
       <c r="R44" t="n">
-        <v>6952925</v>
+        <v>6952605</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5214,15 +5015,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120453401</v>
+        <v>120278811</v>
       </c>
       <c r="B45" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5230,42 +5026,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Österbäck, Hjd</t>
+          <t>A 43789-2024, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385850</v>
+        <v>385294</v>
       </c>
       <c r="R45" t="n">
-        <v>6952827</v>
+        <v>6952914</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5289,12 +5092,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5309,27 +5112,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120454767</v>
+        <v>120443858</v>
       </c>
       <c r="B46" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5337,16 +5135,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5354,25 +5152,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385870</v>
+        <v>385646</v>
       </c>
       <c r="R46" t="n">
-        <v>6952880</v>
+        <v>6952554</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5396,12 +5198,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,15 +5230,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120454959</v>
+        <v>112548768</v>
       </c>
       <c r="B47" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5444,37 +5241,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Österbäck, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385878</v>
+        <v>385355</v>
       </c>
       <c r="R47" t="n">
-        <v>6952882</v>
+        <v>6952780</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5498,12 +5296,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5518,27 +5316,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120454211</v>
+        <v>112556390</v>
       </c>
       <c r="B48" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5546,37 +5339,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385792</v>
+        <v>385551</v>
       </c>
       <c r="R48" t="n">
-        <v>6952933</v>
+        <v>6953318</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5600,12 +5394,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5620,27 +5414,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120454810</v>
+        <v>120442990</v>
       </c>
       <c r="B49" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5648,34 +5437,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Östervallen, Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385870</v>
+        <v>385757</v>
       </c>
       <c r="R49" t="n">
-        <v>6952880</v>
+        <v>6952721</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5702,12 +5491,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5731,541 +5520,6 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>120455648</v>
-      </c>
-      <c r="B50" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Östervallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>385900</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6953028</v>
-      </c>
-      <c r="S50" t="n">
-        <v>4</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>120456569</v>
-      </c>
-      <c r="B51" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Östervallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>385413</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6953117</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>120456761</v>
-      </c>
-      <c r="B52" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Östervallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>385283</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6953005</v>
-      </c>
-      <c r="S52" t="n">
-        <v>4</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>120456719</v>
-      </c>
-      <c r="B53" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Östervallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>385325</v>
-      </c>
-      <c r="R53" t="n">
-        <v>6953048</v>
-      </c>
-      <c r="S53" t="n">
-        <v>4</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>120454913</v>
-      </c>
-      <c r="B54" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Östervallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>385878</v>
-      </c>
-      <c r="R54" t="n">
-        <v>6952882</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43789-2024 artfynd.xlsx
+++ b/artfynd/A 43789-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112549327</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120436944</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,6 +1185,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438518</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1257,6 +1287,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120440707</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1354,6 +1389,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1451,6 +1491,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454959</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120438102</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120439074</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278807</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112548756</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112548735</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112549343</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278809</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2360,6 +2445,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441015</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2457,6 +2547,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441280</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441474</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441648</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2763,6 +2868,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442167</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2865,6 +2975,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442556</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2967,6 +3082,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120443078</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3069,6 +3189,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120443179</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3171,6 +3296,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120443298</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3273,6 +3403,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120452681</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3375,6 +3510,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453401</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3477,6 +3617,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453522</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3579,6 +3724,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453603</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3681,6 +3831,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453824</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3783,6 +3938,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453860</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3885,6 +4045,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120453988</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3987,6 +4152,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454238</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4089,6 +4259,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454767</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4191,6 +4366,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454913</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4293,6 +4473,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455648</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4395,6 +4580,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456291</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4502,6 +4692,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456499</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4604,6 +4799,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456569</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4706,6 +4906,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456581</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4808,6 +5013,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456719</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4910,6 +5120,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456761</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5012,6 +5227,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120457051</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5121,6 +5341,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278811</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5227,6 +5452,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120443858</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5325,6 +5555,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112548768</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5423,6 +5658,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112556390</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5520,8 +5760,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442990</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>